--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1G.1103</t>
+          <t>IG.1103</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mi</t>
+          <t>G</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KIU</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G09H</t>
+          <t>G09D</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G09D</t>
+          <t>G09C</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63029.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
